--- a/output/2026-09-02_08_Italia_Abruzzo_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-02_08_Italia_Abruzzo_Utensilerie_e_Macchine_Utensili.xlsx
@@ -578,7 +578,6 @@
           <t>0862 760389 / 0862 760065</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>ATTENZIONE: il sito attuale è orientato a vendita/posa infissi PVC-legno-alluminio - verificare se l'attività di ferramenta ingrosso è ancora attiva.</t>
@@ -596,7 +595,6 @@
           <t>F.S.Q. Ferramenta Servizi e Qualità di Ahmad Ibrahim e Sajjadi Dario</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>L'Aquila (AQ)</t>
@@ -612,7 +610,6 @@
           <t>0862 414451</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Confermato: commercio ferramenta/utensileria, Via Federico Trecco 3.</t>
@@ -650,7 +647,6 @@
           <t>0863 401040 / 338 7353749</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Confermato: ferramenta, utensili a mano/elettrici, forniture industriali.</t>
@@ -688,7 +684,6 @@
           <t>0863 22720 / 0863 26894</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Confermato: distributore forniture industriali, cuscinetti, trasmissioni, oleodinamica/pneumatica; 42 anni di attività.</t>
@@ -706,7 +701,6 @@
           <t>Ferroutensili di Marcantonio Andrea</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Sulmona (AQ)</t>
@@ -722,7 +716,6 @@
           <t>0864 53622</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Confermato via Europages/directory: distributore utensili a mano/motore e ferramenta, fondata 1994.</t>
@@ -760,7 +753,6 @@
           <t>0864 845831</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Confermato: ferramenta, sistemi di fissaggio, elettroutensili.</t>
@@ -820,7 +812,6 @@
           <t>Piersant di Pierleoni Enrico &amp; C. S.a.s.</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Ovindoli (AQ)</t>
@@ -836,7 +827,6 @@
           <t>0863 705739</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Confermato: ferramenta al dettaglio, Via O. Moretti 78, Ovindoli.</t>
@@ -854,7 +844,6 @@
           <t>3T di Tabacco Andrea</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Tagliacozzo (AQ)</t>
@@ -870,7 +859,6 @@
           <t>0863 610728</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Confermato: ferramenta, Piazza Duca degli Abruzzi 57, Tagliacozzo.</t>
@@ -908,7 +896,6 @@
           <t>0861 210242</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Confermato: distribuzione forniture industriali, macchine utensili, utensileria, organi di trasmissione; 35 anni di attività.</t>
@@ -953,7 +940,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Confermato: ricambi industriali, cuscinetti, trasmissioni, macchine utensili, utensileria.</t>
+          <t>Confermato: ricambi industriali, cuscinetti, trasmissioni, macchine utensili, utensileria. [DUPLICATO — vedi anche: 2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -988,7 +975,6 @@
           <t>0861 743511</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Confermato: storico rivenditore/assistenza macchine utensili, acquisito da CNS Srl nel 2017. Telefono verificato via PagineBianche.</t>
@@ -1033,7 +1019,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Confermato: vendita/assistenza macchine industriali, idropulitrici, elettroutensili.</t>
+          <t>Confermato: vendita/assistenza macchine industriali, idropulitrici, elettroutensili. [DUPLICATO — vedi anche: 2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1110,7 +1096,6 @@
           <t>0861 765469 / 0861 797942</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Confermato: distribuzione ferramenta industriale, utensili, componenti tecnici; gruppo con 3 filiali nazionali.</t>
@@ -1155,7 +1140,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Confermato: cuscinetti, oleodinamica, pneumatica, utensili da taglio; oltre 60 anni di attività, opera su TE/PE/CH/AQ.</t>
+          <t>Confermato: cuscinetti, oleodinamica, pneumatica, utensili da taglio; oltre 60 anni di attività, opera su TE/PE/CH/AQ. [DUPLICATO — vedi anche: 2026-09-02_03_Italia_Abruzzo_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1274,7 +1259,6 @@
           <t>085 4313289</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Confermato: vendita/assistenza utensili e distribuzione ricambi/accessori B2B, ~30 anni di attività.</t>
@@ -1319,7 +1303,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Confermato: forniture tecniche industriali, utensileria, componenti pneumatici, 20 anni di attività.</t>
+          <t>Confermato: forniture tecniche industriali, utensileria, componenti pneumatici, 20 anni di attività. [DUPLICATO — vedi anche: 2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1361,7 +1345,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Confermato: produttore/distributore di levigatrici professionali, utensili diamantati, aspiratori; distributore esclusivo SuperAbrasive Inc.</t>
+          <t>Confermato: produttore/distributore di levigatrici professionali, utensili diamantati, aspiratori; distributore esclusivo SuperAbrasive Inc. [DUPLICATO — vedi anche: 2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1438,7 +1422,6 @@
           <t>085 73346</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Confermato: ferramenta, utensileria, edilizia, colori; azienda familiare dal 1976.</t>
@@ -1518,10 +1501,9 @@
           <t>0871 561812</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Confermato: forniture industriali dal 1974/1977, macchine utensili, cuscinetti, oleodinamica; ~25 dipendenti.</t>
+          <t>Confermato: forniture industriali dal 1974/1977, macchine utensili, cuscinetti, oleodinamica; ~25 dipendenti. [DUPLICATO — vedi anche: 2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1598,7 +1580,6 @@
           <t>0873 37111</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>Confermato: forniture industriali/macchine utensili (torni, fresatrici, robot) dal 1978. Una fonte riporta anche 0873 361900 - verificare.</t>
@@ -1616,7 +1597,6 @@
           <t>Cemu Srl (Centro Macchine Utensili)</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>San Giovanni Teatino (CH) - Sambuceto</t>
@@ -1632,7 +1612,6 @@
           <t>085 4460560</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>Confermato: commercio macchine utensili nuove/usate (torni, fresatrici, trapani, EDM).</t>
@@ -1650,7 +1629,6 @@
           <t>Ferramenta Sa.I.Fer di Andrea Di Prinzio</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>Guardiagrele (CH)</t>
@@ -1666,7 +1644,6 @@
           <t>0871 84883</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Confermato: ferramenta vendita ingrosso/dettaglio, idraulica, sanitari. Una fonte riporta anche 0871 809321 - verificare.</t>
@@ -1704,7 +1681,6 @@
           <t>0873 342319</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Confermato: articoli tecnici e forniture industriali, vendita ingrosso.</t>
@@ -1764,7 +1740,6 @@
           <t>Toracchio S.a.s. (di Toracchio F. &amp; C.)</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>Chieti (CH) - Via per Popoli</t>
@@ -1780,7 +1755,6 @@
           <t>0871 562580</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>Presenza confermata su più directory di settore (forniture industriali). Una fonte riporta anche 0871 441011.</t>
@@ -1860,7 +1834,6 @@
           <t>085 4462462</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>Confermato: ferramenta vendita ingrosso, ATECO commercio ingrosso ferramenta.</t>
@@ -1878,7 +1851,6 @@
           <t>P.R.M. Srl</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>San Giovanni Teatino (CH)</t>
@@ -1894,7 +1866,6 @@
           <t>085 4465257</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>Confermato: macchine utensili - commercio, Via Nenni 274.</t>

--- a/output/2026-09-02_08_Italia_Abruzzo_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-02_08_Italia_Abruzzo_Utensilerie_e_Macchine_Utensili.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
